--- a/data/KatsBaseballTableAssessment.xlsx
+++ b/data/KatsBaseballTableAssessment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rohitkrishnan/Desktop/Liquid Sports Lab/ECCKatsDash/ECCKatsBaseball/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1607CECA-F3F1-5140-A181-D3A935F0B969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307E3050-C23E-6F42-8ECD-4B1B8DC7D888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33460" yWindow="1200" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table Assessment" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="137">
   <si>
     <t xml:space="preserve">Previous Injury </t>
   </si>
@@ -171,9 +171,6 @@
     <t xml:space="preserve">Lateral Shift </t>
   </si>
   <si>
-    <t xml:space="preserve">bilateral ankle fx, scoliosis </t>
-  </si>
-  <si>
     <t>R shoulder bursitis a year ago</t>
   </si>
   <si>
@@ -379,12 +376,6 @@
   </si>
   <si>
     <t>Refermat</t>
-  </si>
-  <si>
-    <t>Brendan</t>
-  </si>
-  <si>
-    <t>Parker</t>
   </si>
   <si>
     <t>Jaden</t>
@@ -789,7 +780,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AE980"/>
+  <dimension ref="A1:AE979"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="18.6640625" customWidth="1"/>
@@ -811,16 +802,16 @@
   <sheetData>
     <row r="1" spans="1:31" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>98</v>
-      </c>
       <c r="C1" s="11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>1</v>
@@ -904,10 +895,10 @@
     </row>
     <row r="2" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="C2" s="6">
         <v>7</v>
@@ -995,10 +986,10 @@
     </row>
     <row r="3" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="C3" s="6">
         <v>8</v>
@@ -1086,10 +1077,10 @@
     </row>
     <row r="4" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="C4" s="6">
         <v>7.5</v>
@@ -1177,10 +1168,10 @@
     </row>
     <row r="5" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="C5" s="6">
         <v>7</v>
@@ -1268,10 +1259,10 @@
     </row>
     <row r="6" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="C6" s="6">
         <v>6</v>
@@ -1362,10 +1353,10 @@
     </row>
     <row r="7" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="C7" s="6">
         <v>9</v>
@@ -1453,10 +1444,10 @@
     </row>
     <row r="8" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="C8" s="6">
         <v>7</v>
@@ -1544,10 +1535,10 @@
     </row>
     <row r="9" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="C9" s="6">
         <v>7</v>
@@ -1635,903 +1626,903 @@
     </row>
     <row r="10" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="6">
+        <v>7</v>
+      </c>
+      <c r="D10" s="7">
+        <v>80</v>
+      </c>
+      <c r="E10" s="2">
+        <v>56</v>
+      </c>
+      <c r="F10" s="2">
+        <v>55</v>
+      </c>
+      <c r="G10" s="2">
+        <v>88</v>
+      </c>
+      <c r="H10" s="2">
+        <v>63</v>
+      </c>
+      <c r="I10" s="2">
+        <v>46</v>
+      </c>
+      <c r="J10" s="2">
+        <v>49</v>
+      </c>
+      <c r="K10" s="2">
+        <v>83</v>
+      </c>
+      <c r="L10" s="2">
+        <v>86</v>
+      </c>
+      <c r="M10" s="2">
+        <v>71</v>
+      </c>
+      <c r="N10" s="2">
+        <v>74</v>
+      </c>
+      <c r="O10" s="2">
+        <f>76+90</f>
+        <v>166</v>
+      </c>
+      <c r="P10" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q10" s="2">
+        <f>48+90</f>
+        <v>138</v>
+      </c>
+      <c r="R10" s="2">
+        <v>110</v>
+      </c>
+      <c r="S10" s="2">
+        <v>60</v>
+      </c>
+      <c r="T10" s="2">
+        <v>65</v>
+      </c>
+      <c r="U10" s="3">
+        <v>40</v>
+      </c>
+      <c r="V10" s="3">
+        <v>43</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC10" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="6">
-        <v>4.5</v>
-      </c>
-      <c r="D10" s="7">
-        <v>128</v>
-      </c>
-      <c r="E10" s="2">
+      <c r="B11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="6">
+        <v>7</v>
+      </c>
+      <c r="D11" s="7">
+        <v>120</v>
+      </c>
+      <c r="E11" s="2">
+        <v>63</v>
+      </c>
+      <c r="F11" s="2">
+        <v>65</v>
+      </c>
+      <c r="G11" s="2">
+        <v>95</v>
+      </c>
+      <c r="H11" s="2">
+        <v>51</v>
+      </c>
+      <c r="I11" s="2">
+        <v>39</v>
+      </c>
+      <c r="J11" s="2">
+        <v>49</v>
+      </c>
+      <c r="K11" s="2">
+        <v>87</v>
+      </c>
+      <c r="L11" s="2">
+        <v>94</v>
+      </c>
+      <c r="M11" s="2">
+        <v>83</v>
+      </c>
+      <c r="N11" s="2">
+        <v>90</v>
+      </c>
+      <c r="O11" s="2">
+        <f>90+90</f>
+        <v>180</v>
+      </c>
+      <c r="P11" s="2">
+        <v>120</v>
+      </c>
+      <c r="Q11" s="2">
+        <f>85+90</f>
+        <v>175</v>
+      </c>
+      <c r="R11" s="2">
+        <v>110</v>
+      </c>
+      <c r="S11" s="2">
+        <v>75</v>
+      </c>
+      <c r="T11" s="2">
+        <v>80</v>
+      </c>
+      <c r="U11" s="3">
+        <v>50</v>
+      </c>
+      <c r="V11" s="3">
+        <v>47</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC11" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="6">
+        <v>7</v>
+      </c>
+      <c r="D12" s="7">
+        <v>64</v>
+      </c>
+      <c r="E12" s="2">
+        <v>68</v>
+      </c>
+      <c r="F12" s="2">
+        <v>65</v>
+      </c>
+      <c r="G12" s="2">
+        <v>73</v>
+      </c>
+      <c r="H12" s="2">
+        <v>51</v>
+      </c>
+      <c r="I12" s="2">
+        <v>46</v>
+      </c>
+      <c r="J12" s="2">
+        <v>65</v>
+      </c>
+      <c r="K12" s="2">
         <v>60</v>
       </c>
-      <c r="F10" s="2">
+      <c r="L12" s="2">
+        <v>68</v>
+      </c>
+      <c r="M12" s="2">
+        <v>56</v>
+      </c>
+      <c r="N12" s="2">
         <v>60</v>
       </c>
-      <c r="G10" s="2">
-        <v>86</v>
-      </c>
-      <c r="H10" s="2">
-        <v>42</v>
-      </c>
-      <c r="I10" s="2">
-        <v>53</v>
-      </c>
-      <c r="J10" s="2">
-        <v>29</v>
-      </c>
-      <c r="K10" s="2">
-        <v>95</v>
-      </c>
-      <c r="L10" s="2">
-        <v>90</v>
-      </c>
-      <c r="M10" s="2">
-        <v>92</v>
-      </c>
-      <c r="N10" s="2">
-        <v>91</v>
-      </c>
-      <c r="O10" s="2">
+      <c r="O12" s="2">
+        <f>67+90</f>
+        <v>157</v>
+      </c>
+      <c r="P12" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q12" s="2">
         <f>35+90</f>
         <v>125</v>
       </c>
-      <c r="P10" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q10" s="4">
-        <f>20+90</f>
+      <c r="R12" s="2">
+        <v>96</v>
+      </c>
+      <c r="S12" s="2">
+        <v>58</v>
+      </c>
+      <c r="T12" s="2">
+        <v>76</v>
+      </c>
+      <c r="U12" s="3">
+        <v>46</v>
+      </c>
+      <c r="V12" s="3">
+        <v>44</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC12" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="D13" s="7">
+        <v>48</v>
+      </c>
+      <c r="E13" s="2">
+        <v>73</v>
+      </c>
+      <c r="F13" s="2">
+        <v>88</v>
+      </c>
+      <c r="G13" s="2">
+        <v>75</v>
+      </c>
+      <c r="H13" s="2">
+        <v>45</v>
+      </c>
+      <c r="I13" s="2">
+        <v>46</v>
+      </c>
+      <c r="J13" s="2">
+        <v>36</v>
+      </c>
+      <c r="K13" s="2">
+        <v>64</v>
+      </c>
+      <c r="L13" s="2">
+        <v>69</v>
+      </c>
+      <c r="M13" s="2">
+        <v>53</v>
+      </c>
+      <c r="N13" s="2">
+        <v>57</v>
+      </c>
+      <c r="O13" s="2">
+        <f>58+90</f>
+        <v>148</v>
+      </c>
+      <c r="P13" s="2">
         <v>110</v>
       </c>
-      <c r="R10" s="2">
+      <c r="Q13" s="2">
+        <f>40+90</f>
+        <v>130</v>
+      </c>
+      <c r="R13" s="2">
+        <v>115</v>
+      </c>
+      <c r="S13" s="2">
+        <v>66</v>
+      </c>
+      <c r="T13" s="2">
+        <v>73</v>
+      </c>
+      <c r="U13" s="3">
+        <v>42</v>
+      </c>
+      <c r="V13" s="3">
+        <v>34</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC13" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="6">
+        <v>8</v>
+      </c>
+      <c r="D14" s="7">
+        <v>169</v>
+      </c>
+      <c r="E14" s="2">
+        <v>65</v>
+      </c>
+      <c r="F14" s="2">
+        <v>51</v>
+      </c>
+      <c r="G14" s="2">
         <v>83</v>
       </c>
-      <c r="S10" s="2">
-        <v>60</v>
-      </c>
-      <c r="T10" s="2">
-        <v>65</v>
-      </c>
-      <c r="U10" s="3">
-        <v>46</v>
-      </c>
-      <c r="V10" s="3">
-        <v>42</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="X10" s="2" t="s">
+      <c r="H14" s="2">
         <v>44</v>
       </c>
-      <c r="Y10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC10" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C11" s="6">
-        <v>7</v>
-      </c>
-      <c r="D11" s="7">
-        <v>80</v>
-      </c>
-      <c r="E11" s="2">
-        <v>56</v>
-      </c>
-      <c r="F11" s="2">
-        <v>55</v>
-      </c>
-      <c r="G11" s="2">
-        <v>88</v>
-      </c>
-      <c r="H11" s="2">
-        <v>63</v>
-      </c>
-      <c r="I11" s="2">
-        <v>46</v>
-      </c>
-      <c r="J11" s="2">
-        <v>49</v>
-      </c>
-      <c r="K11" s="2">
-        <v>83</v>
-      </c>
-      <c r="L11" s="2">
-        <v>86</v>
-      </c>
-      <c r="M11" s="2">
-        <v>71</v>
-      </c>
-      <c r="N11" s="2">
-        <v>74</v>
-      </c>
-      <c r="O11" s="2">
-        <f>76+90</f>
-        <v>166</v>
-      </c>
-      <c r="P11" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q11" s="2">
+      <c r="I14" s="2">
+        <v>43</v>
+      </c>
+      <c r="J14" s="2">
+        <v>47</v>
+      </c>
+      <c r="K14" s="2">
+        <v>64</v>
+      </c>
+      <c r="L14" s="2">
+        <v>64</v>
+      </c>
+      <c r="M14" s="2">
+        <v>54</v>
+      </c>
+      <c r="N14" s="2">
+        <v>48</v>
+      </c>
+      <c r="O14" s="2">
+        <f>25+90</f>
+        <v>115</v>
+      </c>
+      <c r="P14" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q14" s="2">
         <f>48+90</f>
         <v>138</v>
       </c>
-      <c r="R11" s="2">
+      <c r="R14" s="2">
         <v>110</v>
       </c>
-      <c r="S11" s="2">
+      <c r="S14" s="2">
+        <v>64</v>
+      </c>
+      <c r="T14" s="2">
+        <v>74</v>
+      </c>
+      <c r="U14" s="3">
+        <v>43</v>
+      </c>
+      <c r="V14" s="3">
+        <v>46</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC14" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="6">
+        <v>8</v>
+      </c>
+      <c r="D15" s="7">
+        <v>90</v>
+      </c>
+      <c r="E15" s="2">
+        <v>64</v>
+      </c>
+      <c r="F15" s="2">
         <v>60</v>
       </c>
-      <c r="T11" s="2">
+      <c r="G15" s="2">
+        <v>83</v>
+      </c>
+      <c r="H15" s="2">
+        <v>54</v>
+      </c>
+      <c r="I15" s="2">
+        <v>50</v>
+      </c>
+      <c r="J15" s="2">
+        <v>56</v>
+      </c>
+      <c r="K15" s="2">
+        <v>70</v>
+      </c>
+      <c r="L15" s="2">
+        <v>67</v>
+      </c>
+      <c r="M15" s="2">
+        <v>70</v>
+      </c>
+      <c r="N15" s="2">
+        <v>66</v>
+      </c>
+      <c r="O15" s="2">
+        <f>54+90</f>
+        <v>144</v>
+      </c>
+      <c r="P15" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q15" s="2">
+        <f>59+90</f>
+        <v>149</v>
+      </c>
+      <c r="R15" s="2">
+        <v>105</v>
+      </c>
+      <c r="S15" s="2">
+        <v>68</v>
+      </c>
+      <c r="T15" s="2">
+        <v>64</v>
+      </c>
+      <c r="U15" s="3">
+        <v>46</v>
+      </c>
+      <c r="V15" s="3">
+        <v>38</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC15" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="6">
+        <v>9</v>
+      </c>
+      <c r="D16" s="7">
+        <v>128</v>
+      </c>
+      <c r="E16" s="2">
+        <v>75</v>
+      </c>
+      <c r="F16" s="2">
+        <v>74</v>
+      </c>
+      <c r="G16" s="2">
+        <v>74</v>
+      </c>
+      <c r="H16" s="2">
+        <v>54</v>
+      </c>
+      <c r="I16" s="2">
+        <v>43</v>
+      </c>
+      <c r="J16" s="2">
+        <v>45</v>
+      </c>
+      <c r="K16" s="2">
+        <v>56</v>
+      </c>
+      <c r="L16" s="2">
         <v>65</v>
       </c>
-      <c r="U11" s="3">
+      <c r="M16" s="2">
+        <v>59</v>
+      </c>
+      <c r="N16" s="2">
+        <v>62</v>
+      </c>
+      <c r="O16" s="2">
+        <f>44+90</f>
+        <v>134</v>
+      </c>
+      <c r="P16" s="2">
+        <v>86</v>
+      </c>
+      <c r="Q16" s="2">
+        <f>43+90</f>
+        <v>133</v>
+      </c>
+      <c r="R16" s="2">
+        <v>110</v>
+      </c>
+      <c r="S16" s="2">
+        <v>60</v>
+      </c>
+      <c r="T16" s="2">
+        <v>72</v>
+      </c>
+      <c r="U16" s="3">
+        <v>43</v>
+      </c>
+      <c r="V16" s="3">
+        <v>41</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC16" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="6">
+        <v>8</v>
+      </c>
+      <c r="D17" s="7">
+        <v>118</v>
+      </c>
+      <c r="E17" s="2">
+        <v>70</v>
+      </c>
+      <c r="F17" s="2">
+        <v>75</v>
+      </c>
+      <c r="G17" s="2">
+        <v>70</v>
+      </c>
+      <c r="H17" s="2">
+        <v>52</v>
+      </c>
+      <c r="I17" s="2">
+        <v>45</v>
+      </c>
+      <c r="J17" s="2">
+        <v>45</v>
+      </c>
+      <c r="K17" s="2">
+        <v>71</v>
+      </c>
+      <c r="L17" s="2">
+        <v>71</v>
+      </c>
+      <c r="M17" s="2">
+        <v>64</v>
+      </c>
+      <c r="N17" s="2">
+        <v>66</v>
+      </c>
+      <c r="O17" s="4">
+        <f>50+90</f>
+        <v>140</v>
+      </c>
+      <c r="P17" s="2">
+        <v>105</v>
+      </c>
+      <c r="Q17" s="2">
+        <f>46+90</f>
+        <v>136</v>
+      </c>
+      <c r="R17" s="2">
+        <v>115</v>
+      </c>
+      <c r="S17" s="2">
+        <v>44</v>
+      </c>
+      <c r="T17" s="2">
+        <v>58</v>
+      </c>
+      <c r="U17" s="3">
+        <v>45</v>
+      </c>
+      <c r="V17" s="3">
+        <v>45</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="V11" s="3">
+      <c r="Y17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC17" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="6">
+        <v>6.5</v>
+      </c>
+      <c r="D18" s="7">
+        <v>64</v>
+      </c>
+      <c r="E18" s="2">
+        <v>74</v>
+      </c>
+      <c r="F18" s="2">
+        <v>69</v>
+      </c>
+      <c r="G18" s="2">
+        <v>86</v>
+      </c>
+      <c r="H18" s="2">
+        <v>67</v>
+      </c>
+      <c r="I18" s="2">
         <v>43</v>
       </c>
-      <c r="W11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="X11" s="2" t="s">
+      <c r="J18" s="2">
+        <v>32</v>
+      </c>
+      <c r="K18" s="2">
+        <v>62</v>
+      </c>
+      <c r="L18" s="2">
+        <v>67</v>
+      </c>
+      <c r="M18" s="2">
+        <v>61</v>
+      </c>
+      <c r="N18" s="2">
+        <v>60</v>
+      </c>
+      <c r="O18" s="2">
+        <f>53+90</f>
+        <v>143</v>
+      </c>
+      <c r="P18" s="2">
+        <v>69</v>
+      </c>
+      <c r="Q18" s="2">
+        <f>39+90</f>
+        <v>129</v>
+      </c>
+      <c r="R18" s="2">
+        <v>89</v>
+      </c>
+      <c r="S18" s="2">
+        <v>45</v>
+      </c>
+      <c r="T18" s="2">
+        <v>60</v>
+      </c>
+      <c r="U18" s="3">
+        <v>37</v>
+      </c>
+      <c r="V18" s="3">
+        <v>37</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="X18" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Y11" s="2" t="s">
+      <c r="Y18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Z11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA11" s="2" t="s">
+      <c r="Z18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AB11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC11" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C12" s="6">
-        <v>7</v>
-      </c>
-      <c r="D12" s="7">
-        <v>120</v>
-      </c>
-      <c r="E12" s="2">
-        <v>63</v>
-      </c>
-      <c r="F12" s="2">
-        <v>65</v>
-      </c>
-      <c r="G12" s="2">
-        <v>95</v>
-      </c>
-      <c r="H12" s="2">
-        <v>51</v>
-      </c>
-      <c r="I12" s="2">
-        <v>39</v>
-      </c>
-      <c r="J12" s="2">
-        <v>49</v>
-      </c>
-      <c r="K12" s="2">
+      <c r="AA18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC18" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="6">
+        <v>9</v>
+      </c>
+      <c r="D19" s="7">
+        <v>128</v>
+      </c>
+      <c r="E19" s="2">
+        <v>70</v>
+      </c>
+      <c r="F19" s="2">
+        <v>74</v>
+      </c>
+      <c r="G19" s="2">
+        <v>90</v>
+      </c>
+      <c r="H19" s="2">
+        <v>44</v>
+      </c>
+      <c r="I19" s="2">
+        <v>50</v>
+      </c>
+      <c r="J19" s="2">
+        <v>56</v>
+      </c>
+      <c r="K19" s="2">
         <v>87</v>
       </c>
-      <c r="L12" s="2">
-        <v>94</v>
-      </c>
-      <c r="M12" s="2">
+      <c r="L19" s="2">
+        <v>86</v>
+      </c>
+      <c r="M19" s="2">
         <v>83</v>
       </c>
-      <c r="N12" s="2">
-        <v>90</v>
-      </c>
-      <c r="O12" s="2">
-        <f>90+90</f>
-        <v>180</v>
-      </c>
-      <c r="P12" s="2">
-        <v>120</v>
-      </c>
-      <c r="Q12" s="2">
-        <f>85+90</f>
-        <v>175</v>
-      </c>
-      <c r="R12" s="2">
+      <c r="N19" s="2">
+        <v>84</v>
+      </c>
+      <c r="O19" s="2">
+        <f>41+90</f>
+        <v>131</v>
+      </c>
+      <c r="P19" s="2">
         <v>110</v>
       </c>
-      <c r="S12" s="2">
-        <v>75</v>
-      </c>
-      <c r="T12" s="2">
-        <v>80</v>
-      </c>
-      <c r="U12" s="3">
-        <v>50</v>
-      </c>
-      <c r="V12" s="3">
-        <v>47</v>
-      </c>
-      <c r="W12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="X12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC12" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" s="6">
-        <v>7</v>
-      </c>
-      <c r="D13" s="7">
-        <v>64</v>
-      </c>
-      <c r="E13" s="2">
-        <v>68</v>
-      </c>
-      <c r="F13" s="2">
-        <v>65</v>
-      </c>
-      <c r="G13" s="2">
-        <v>73</v>
-      </c>
-      <c r="H13" s="2">
-        <v>51</v>
-      </c>
-      <c r="I13" s="2">
-        <v>46</v>
-      </c>
-      <c r="J13" s="2">
-        <v>65</v>
-      </c>
-      <c r="K13" s="2">
-        <v>60</v>
-      </c>
-      <c r="L13" s="2">
-        <v>68</v>
-      </c>
-      <c r="M13" s="2">
-        <v>56</v>
-      </c>
-      <c r="N13" s="2">
-        <v>60</v>
-      </c>
-      <c r="O13" s="2">
-        <f>67+90</f>
-        <v>157</v>
-      </c>
-      <c r="P13" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q13" s="2">
-        <f>35+90</f>
-        <v>125</v>
-      </c>
-      <c r="R13" s="2">
-        <v>96</v>
-      </c>
-      <c r="S13" s="2">
-        <v>58</v>
-      </c>
-      <c r="T13" s="2">
-        <v>76</v>
-      </c>
-      <c r="U13" s="3">
-        <v>46</v>
-      </c>
-      <c r="V13" s="3">
-        <v>44</v>
-      </c>
-      <c r="W13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="X13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC13" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C14" s="6">
-        <v>9.5</v>
-      </c>
-      <c r="D14" s="7">
-        <v>48</v>
-      </c>
-      <c r="E14" s="2">
-        <v>73</v>
-      </c>
-      <c r="F14" s="2">
-        <v>88</v>
-      </c>
-      <c r="G14" s="2">
-        <v>75</v>
-      </c>
-      <c r="H14" s="2">
-        <v>45</v>
-      </c>
-      <c r="I14" s="2">
-        <v>46</v>
-      </c>
-      <c r="J14" s="2">
-        <v>36</v>
-      </c>
-      <c r="K14" s="2">
-        <v>64</v>
-      </c>
-      <c r="L14" s="2">
-        <v>69</v>
-      </c>
-      <c r="M14" s="2">
-        <v>53</v>
-      </c>
-      <c r="N14" s="2">
-        <v>57</v>
-      </c>
-      <c r="O14" s="2">
-        <f>58+90</f>
-        <v>148</v>
-      </c>
-      <c r="P14" s="2">
-        <v>110</v>
-      </c>
-      <c r="Q14" s="2">
+      <c r="Q19" s="2">
         <f>40+90</f>
         <v>130</v>
       </c>
-      <c r="R14" s="2">
+      <c r="R19" s="2">
         <v>115</v>
       </c>
-      <c r="S14" s="2">
-        <v>66</v>
-      </c>
-      <c r="T14" s="2">
-        <v>73</v>
-      </c>
-      <c r="U14" s="3">
-        <v>42</v>
-      </c>
-      <c r="V14" s="3">
-        <v>34</v>
-      </c>
-      <c r="W14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="X14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC14" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15" s="6">
-        <v>8</v>
-      </c>
-      <c r="D15" s="7">
-        <v>169</v>
-      </c>
-      <c r="E15" s="2">
-        <v>65</v>
-      </c>
-      <c r="F15" s="2">
-        <v>51</v>
-      </c>
-      <c r="G15" s="2">
-        <v>83</v>
-      </c>
-      <c r="H15" s="2">
-        <v>44</v>
-      </c>
-      <c r="I15" s="2">
-        <v>43</v>
-      </c>
-      <c r="J15" s="2">
-        <v>47</v>
-      </c>
-      <c r="K15" s="2">
-        <v>64</v>
-      </c>
-      <c r="L15" s="2">
-        <v>64</v>
-      </c>
-      <c r="M15" s="2">
-        <v>54</v>
-      </c>
-      <c r="N15" s="2">
-        <v>48</v>
-      </c>
-      <c r="O15" s="2">
-        <f>25+90</f>
-        <v>115</v>
-      </c>
-      <c r="P15" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q15" s="2">
-        <f>48+90</f>
-        <v>138</v>
-      </c>
-      <c r="R15" s="2">
-        <v>110</v>
-      </c>
-      <c r="S15" s="2">
-        <v>64</v>
-      </c>
-      <c r="T15" s="2">
-        <v>74</v>
-      </c>
-      <c r="U15" s="3">
-        <v>43</v>
-      </c>
-      <c r="V15" s="3">
-        <v>46</v>
-      </c>
-      <c r="W15" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="X15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC15" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C16" s="6">
-        <v>8</v>
-      </c>
-      <c r="D16" s="7">
-        <v>90</v>
-      </c>
-      <c r="E16" s="2">
-        <v>64</v>
-      </c>
-      <c r="F16" s="2">
-        <v>60</v>
-      </c>
-      <c r="G16" s="2">
-        <v>83</v>
-      </c>
-      <c r="H16" s="2">
-        <v>54</v>
-      </c>
-      <c r="I16" s="2">
-        <v>50</v>
-      </c>
-      <c r="J16" s="2">
-        <v>56</v>
-      </c>
-      <c r="K16" s="2">
-        <v>70</v>
-      </c>
-      <c r="L16" s="2">
-        <v>67</v>
-      </c>
-      <c r="M16" s="2">
-        <v>70</v>
-      </c>
-      <c r="N16" s="2">
-        <v>66</v>
-      </c>
-      <c r="O16" s="2">
-        <f>54+90</f>
-        <v>144</v>
-      </c>
-      <c r="P16" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q16" s="2">
-        <f>59+90</f>
-        <v>149</v>
-      </c>
-      <c r="R16" s="2">
-        <v>105</v>
-      </c>
-      <c r="S16" s="2">
-        <v>68</v>
-      </c>
-      <c r="T16" s="2">
-        <v>64</v>
-      </c>
-      <c r="U16" s="3">
-        <v>46</v>
-      </c>
-      <c r="V16" s="3">
-        <v>38</v>
-      </c>
-      <c r="W16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="X16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC16" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C17" s="6">
-        <v>9</v>
-      </c>
-      <c r="D17" s="7">
-        <v>128</v>
-      </c>
-      <c r="E17" s="2">
-        <v>75</v>
-      </c>
-      <c r="F17" s="2">
-        <v>74</v>
-      </c>
-      <c r="G17" s="2">
-        <v>74</v>
-      </c>
-      <c r="H17" s="2">
-        <v>54</v>
-      </c>
-      <c r="I17" s="2">
-        <v>43</v>
-      </c>
-      <c r="J17" s="2">
-        <v>45</v>
-      </c>
-      <c r="K17" s="2">
-        <v>56</v>
-      </c>
-      <c r="L17" s="2">
-        <v>65</v>
-      </c>
-      <c r="M17" s="2">
-        <v>59</v>
-      </c>
-      <c r="N17" s="2">
-        <v>62</v>
-      </c>
-      <c r="O17" s="2">
-        <f>44+90</f>
-        <v>134</v>
-      </c>
-      <c r="P17" s="2">
-        <v>86</v>
-      </c>
-      <c r="Q17" s="2">
-        <f>43+90</f>
-        <v>133</v>
-      </c>
-      <c r="R17" s="2">
-        <v>110</v>
-      </c>
-      <c r="S17" s="2">
-        <v>60</v>
-      </c>
-      <c r="T17" s="2">
-        <v>72</v>
-      </c>
-      <c r="U17" s="3">
-        <v>43</v>
-      </c>
-      <c r="V17" s="3">
-        <v>41</v>
-      </c>
-      <c r="W17" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="X17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB17" s="2" t="s">
+      <c r="S19" s="2">
+        <v>81</v>
+      </c>
+      <c r="T19" s="2">
+        <v>78</v>
+      </c>
+      <c r="U19" s="3">
+        <v>36</v>
+      </c>
+      <c r="V19" s="3">
         <v>35</v>
-      </c>
-      <c r="AC17" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C18" s="6">
-        <v>8</v>
-      </c>
-      <c r="D18" s="7">
-        <v>118</v>
-      </c>
-      <c r="E18" s="2">
-        <v>70</v>
-      </c>
-      <c r="F18" s="2">
-        <v>75</v>
-      </c>
-      <c r="G18" s="2">
-        <v>70</v>
-      </c>
-      <c r="H18" s="2">
-        <v>52</v>
-      </c>
-      <c r="I18" s="2">
-        <v>45</v>
-      </c>
-      <c r="J18" s="2">
-        <v>45</v>
-      </c>
-      <c r="K18" s="2">
-        <v>71</v>
-      </c>
-      <c r="L18" s="2">
-        <v>71</v>
-      </c>
-      <c r="M18" s="2">
-        <v>64</v>
-      </c>
-      <c r="N18" s="2">
-        <v>66</v>
-      </c>
-      <c r="O18" s="4">
-        <f>50+90</f>
-        <v>140</v>
-      </c>
-      <c r="P18" s="2">
-        <v>105</v>
-      </c>
-      <c r="Q18" s="2">
-        <f>46+90</f>
-        <v>136</v>
-      </c>
-      <c r="R18" s="2">
-        <v>115</v>
-      </c>
-      <c r="S18" s="2">
-        <v>44</v>
-      </c>
-      <c r="T18" s="2">
-        <v>58</v>
-      </c>
-      <c r="U18" s="3">
-        <v>45</v>
-      </c>
-      <c r="V18" s="3">
-        <v>45</v>
-      </c>
-      <c r="W18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X18" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC18" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C19" s="6">
-        <v>6.5</v>
-      </c>
-      <c r="D19" s="7">
-        <v>64</v>
-      </c>
-      <c r="E19" s="2">
-        <v>74</v>
-      </c>
-      <c r="F19" s="2">
-        <v>69</v>
-      </c>
-      <c r="G19" s="2">
-        <v>86</v>
-      </c>
-      <c r="H19" s="2">
-        <v>67</v>
-      </c>
-      <c r="I19" s="2">
-        <v>43</v>
-      </c>
-      <c r="J19" s="2">
-        <v>32</v>
-      </c>
-      <c r="K19" s="2">
-        <v>62</v>
-      </c>
-      <c r="L19" s="2">
-        <v>67</v>
-      </c>
-      <c r="M19" s="2">
-        <v>61</v>
-      </c>
-      <c r="N19" s="2">
-        <v>60</v>
-      </c>
-      <c r="O19" s="2">
-        <f>53+90</f>
-        <v>143</v>
-      </c>
-      <c r="P19" s="2">
-        <v>69</v>
-      </c>
-      <c r="Q19" s="2">
-        <f>39+90</f>
-        <v>129</v>
-      </c>
-      <c r="R19" s="2">
-        <v>89</v>
-      </c>
-      <c r="S19" s="2">
-        <v>45</v>
-      </c>
-      <c r="T19" s="2">
-        <v>60</v>
-      </c>
-      <c r="U19" s="3">
-        <v>37</v>
-      </c>
-      <c r="V19" s="3">
-        <v>37</v>
       </c>
       <c r="W19" s="1" t="s">
         <v>55</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="Y19" s="2" t="s">
         <v>28</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA19" s="2" t="s">
         <v>30</v>
@@ -2544,95 +2535,8 @@
       </c>
     </row>
     <row r="20" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C20" s="6">
-        <v>9</v>
-      </c>
-      <c r="D20" s="7">
-        <v>128</v>
-      </c>
-      <c r="E20" s="2">
-        <v>70</v>
-      </c>
-      <c r="F20" s="2">
-        <v>74</v>
-      </c>
-      <c r="G20" s="2">
-        <v>90</v>
-      </c>
-      <c r="H20" s="2">
-        <v>44</v>
-      </c>
-      <c r="I20" s="2">
-        <v>50</v>
-      </c>
-      <c r="J20" s="2">
-        <v>56</v>
-      </c>
-      <c r="K20" s="2">
-        <v>87</v>
-      </c>
-      <c r="L20" s="2">
-        <v>86</v>
-      </c>
-      <c r="M20" s="2">
-        <v>83</v>
-      </c>
-      <c r="N20" s="2">
-        <v>84</v>
-      </c>
-      <c r="O20" s="2">
-        <f>41+90</f>
-        <v>131</v>
-      </c>
-      <c r="P20" s="2">
-        <v>110</v>
-      </c>
-      <c r="Q20" s="2">
-        <f>40+90</f>
-        <v>130</v>
-      </c>
-      <c r="R20" s="2">
-        <v>115</v>
-      </c>
-      <c r="S20" s="2">
-        <v>81</v>
-      </c>
-      <c r="T20" s="2">
-        <v>78</v>
-      </c>
-      <c r="U20" s="3">
-        <v>36</v>
-      </c>
-      <c r="V20" s="3">
-        <v>35</v>
-      </c>
-      <c r="W20" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="X20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC20" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
     </row>
     <row r="21" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="U21" s="3"/>
@@ -2762,7 +2666,7 @@
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
     </row>
-    <row r="53" spans="21:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="21:22" ht="13" x14ac:dyDescent="0.15">
       <c r="U53" s="3"/>
       <c r="V53" s="3"/>
     </row>
@@ -6470,22 +6374,18 @@
       <c r="U979" s="3"/>
       <c r="V979" s="3"/>
     </row>
-    <row r="980" spans="21:22" ht="13" x14ac:dyDescent="0.15">
-      <c r="U980" s="3"/>
-      <c r="V980" s="3"/>
-    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X2:X20" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X2:X19" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Good Rotation,Lateral Shift ,Unable "</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AB2:AC20" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AB2:AC19" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Good,Trunk Stability ,LE Stability "</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y2:Y20" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y2:Y19" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Good,Shake &amp; Bake,No Posterior Tilt ,No Anterior Tilt"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z2:AA20" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z2:AA19" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Good,Knee Valgus - Foot/hip,Poor Eccentric Control"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6498,7 +6398,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z128"/>
+  <dimension ref="A1:Z127"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -6508,26 +6408,26 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="e">
-        <f>A3:A21</f>
+        <f>A3:A20</f>
         <v>#VALUE!</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -6555,22 +6455,22 @@
         <v>Nick</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6579,22 +6479,22 @@
         <v>Xavier</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6603,22 +6503,22 @@
         <v>John</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="G4" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6627,22 +6527,22 @@
         <v>Joe</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6651,22 +6551,22 @@
         <v>Liam</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6675,22 +6575,22 @@
         <v>Rafael</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6699,22 +6599,22 @@
         <v>Jaxzyn</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6723,821 +6623,530 @@
         <v>Justin</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="D9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="str">
         <f>'Table Assessment'!A10</f>
-        <v>Brendan</v>
+        <v>Jaden</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="str">
         <f>'Table Assessment'!A11</f>
-        <v>Jaden</v>
+        <v>Kayden</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="str">
         <f>'Table Assessment'!A12</f>
-        <v>Kayden</v>
+        <v>Kaleb</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="str">
         <f>'Table Assessment'!A13</f>
-        <v>Kaleb</v>
+        <v>Tony</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="str">
         <f>'Table Assessment'!A14</f>
-        <v>Tony</v>
+        <v>Kieran</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="str">
         <f>'Table Assessment'!A15</f>
-        <v>Kieran</v>
+        <v>Zack</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="str">
         <f>'Table Assessment'!A16</f>
-        <v>Zack</v>
+        <v>Gianluca</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="str">
         <f>'Table Assessment'!A17</f>
-        <v>Gianluca</v>
+        <v>Cole</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="G17" s="2" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="str">
         <f>'Table Assessment'!A18</f>
-        <v>Cole</v>
+        <v>Reece</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="str">
         <f>'Table Assessment'!A19</f>
-        <v>Reece</v>
+        <v>Caleb</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="2" t="str">
-        <f>'Table Assessment'!A20</f>
-        <v>Caleb</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>73</v>
-      </c>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="2"/>
     </row>
     <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="2">
-        <f>'Table Assessment'!A21</f>
-        <v>0</v>
-      </c>
+      <c r="A40" s="2"/>
     </row>
     <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="2">
-        <f>'Table Assessment'!A22</f>
-        <v>0</v>
-      </c>
+      <c r="A41" s="2"/>
     </row>
     <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="2">
-        <f>'Table Assessment'!A23</f>
-        <v>0</v>
-      </c>
+      <c r="A42" s="2"/>
     </row>
     <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="2">
-        <f>'Table Assessment'!A24</f>
-        <v>0</v>
-      </c>
+      <c r="A43" s="2"/>
     </row>
     <row r="44" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="2">
-        <f>'Table Assessment'!A25</f>
-        <v>0</v>
-      </c>
+      <c r="A44" s="2"/>
     </row>
     <row r="45" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="2">
-        <f>'Table Assessment'!A26</f>
-        <v>0</v>
-      </c>
+      <c r="A45" s="2"/>
     </row>
     <row r="46" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="2">
-        <f>'Table Assessment'!A27</f>
-        <v>0</v>
-      </c>
+      <c r="A46" s="2"/>
     </row>
     <row r="47" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="2">
-        <f>'Table Assessment'!A28</f>
-        <v>0</v>
-      </c>
+      <c r="A47" s="2"/>
     </row>
     <row r="48" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="2">
-        <f>'Table Assessment'!A29</f>
-        <v>0</v>
-      </c>
+      <c r="A48" s="2"/>
     </row>
     <row r="49" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="2">
-        <f>'Table Assessment'!A30</f>
-        <v>0</v>
-      </c>
+      <c r="A49" s="2"/>
     </row>
     <row r="50" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="2">
-        <f>'Table Assessment'!A31</f>
-        <v>0</v>
-      </c>
+      <c r="A50" s="2"/>
     </row>
     <row r="51" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="2">
-        <f>'Table Assessment'!A32</f>
-        <v>0</v>
-      </c>
+      <c r="A51" s="2"/>
     </row>
     <row r="52" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="2">
-        <f>'Table Assessment'!A33</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="2">
-        <f>'Table Assessment'!A34</f>
-        <v>0</v>
-      </c>
+      <c r="A52" s="2"/>
+    </row>
+    <row r="53" spans="1:1" ht="13" x14ac:dyDescent="0.15">
+      <c r="A53" s="2"/>
     </row>
     <row r="54" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A54" s="2">
-        <f>'Table Assessment'!A35</f>
-        <v>0</v>
-      </c>
+      <c r="A54" s="2"/>
     </row>
     <row r="55" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A55" s="2">
-        <f>'Table Assessment'!A36</f>
-        <v>0</v>
-      </c>
+      <c r="A55" s="2"/>
     </row>
     <row r="56" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A56" s="2">
-        <f>'Table Assessment'!A37</f>
-        <v>0</v>
-      </c>
+      <c r="A56" s="2"/>
     </row>
     <row r="57" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A57" s="2">
-        <f>'Table Assessment'!A38</f>
-        <v>0</v>
-      </c>
+      <c r="A57" s="2"/>
     </row>
     <row r="58" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A58" s="2">
-        <f>'Table Assessment'!A39</f>
-        <v>0</v>
-      </c>
+      <c r="A58" s="2"/>
     </row>
     <row r="59" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A59" s="2">
-        <f>'Table Assessment'!A40</f>
-        <v>0</v>
-      </c>
+      <c r="A59" s="2"/>
     </row>
     <row r="60" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A60" s="2">
-        <f>'Table Assessment'!A41</f>
-        <v>0</v>
-      </c>
+      <c r="A60" s="2"/>
     </row>
     <row r="61" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A61" s="2">
-        <f>'Table Assessment'!A42</f>
-        <v>0</v>
-      </c>
+      <c r="A61" s="2"/>
     </row>
     <row r="62" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A62" s="2">
-        <f>'Table Assessment'!A43</f>
-        <v>0</v>
-      </c>
+      <c r="A62" s="2"/>
     </row>
     <row r="63" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A63" s="2">
-        <f>'Table Assessment'!A44</f>
-        <v>0</v>
-      </c>
+      <c r="A63" s="2"/>
     </row>
     <row r="64" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A64" s="2">
-        <f>'Table Assessment'!A45</f>
-        <v>0</v>
-      </c>
+      <c r="A64" s="2"/>
     </row>
     <row r="65" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A65" s="2">
-        <f>'Table Assessment'!A46</f>
-        <v>0</v>
-      </c>
+      <c r="A65" s="2"/>
     </row>
     <row r="66" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A66" s="2">
-        <f>'Table Assessment'!A47</f>
-        <v>0</v>
-      </c>
+      <c r="A66" s="2"/>
     </row>
     <row r="67" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A67" s="2">
-        <f>'Table Assessment'!A48</f>
-        <v>0</v>
-      </c>
+      <c r="A67" s="2"/>
     </row>
     <row r="68" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A68" s="2">
-        <f>'Table Assessment'!A49</f>
-        <v>0</v>
-      </c>
+      <c r="A68" s="2"/>
     </row>
     <row r="69" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A69" s="2">
-        <f>'Table Assessment'!A50</f>
-        <v>0</v>
-      </c>
+      <c r="A69" s="2"/>
     </row>
     <row r="70" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A70" s="2">
-        <f>'Table Assessment'!A51</f>
-        <v>0</v>
-      </c>
+      <c r="A70" s="2"/>
     </row>
     <row r="71" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A71" s="2">
-        <f>'Table Assessment'!A52</f>
-        <v>0</v>
-      </c>
+      <c r="A71" s="2"/>
     </row>
     <row r="72" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A72" s="2">
-        <f>'Table Assessment'!A53</f>
-        <v>0</v>
-      </c>
+      <c r="A72" s="2"/>
     </row>
     <row r="73" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A73" s="2">
-        <f>'Table Assessment'!A54</f>
-        <v>0</v>
-      </c>
+      <c r="A73" s="2"/>
     </row>
     <row r="74" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A74" s="2">
-        <f>'Table Assessment'!A55</f>
-        <v>0</v>
-      </c>
+      <c r="A74" s="2"/>
     </row>
     <row r="75" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A75" s="2">
-        <f>'Table Assessment'!A56</f>
-        <v>0</v>
-      </c>
+      <c r="A75" s="2"/>
     </row>
     <row r="76" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A76" s="2">
-        <f>'Table Assessment'!A57</f>
-        <v>0</v>
-      </c>
+      <c r="A76" s="2"/>
     </row>
     <row r="77" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A77" s="2">
-        <f>'Table Assessment'!A58</f>
-        <v>0</v>
-      </c>
+      <c r="A77" s="2"/>
     </row>
     <row r="78" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A78" s="2">
-        <f>'Table Assessment'!A59</f>
-        <v>0</v>
-      </c>
+      <c r="A78" s="2"/>
     </row>
     <row r="79" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A79" s="2">
-        <f>'Table Assessment'!A60</f>
-        <v>0</v>
-      </c>
+      <c r="A79" s="2"/>
     </row>
     <row r="80" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A80" s="2">
-        <f>'Table Assessment'!A61</f>
-        <v>0</v>
-      </c>
+      <c r="A80" s="2"/>
     </row>
     <row r="81" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A81" s="2">
-        <f>'Table Assessment'!A62</f>
-        <v>0</v>
-      </c>
+      <c r="A81" s="2"/>
     </row>
     <row r="82" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A82" s="2">
-        <f>'Table Assessment'!A63</f>
-        <v>0</v>
-      </c>
+      <c r="A82" s="2"/>
     </row>
     <row r="83" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A83" s="2">
-        <f>'Table Assessment'!A64</f>
-        <v>0</v>
-      </c>
+      <c r="A83" s="2"/>
     </row>
     <row r="84" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A84" s="2">
-        <f>'Table Assessment'!A65</f>
-        <v>0</v>
-      </c>
+      <c r="A84" s="2"/>
     </row>
     <row r="85" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A85" s="2">
-        <f>'Table Assessment'!A66</f>
-        <v>0</v>
-      </c>
+      <c r="A85" s="2"/>
     </row>
     <row r="86" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A86" s="2">
-        <f>'Table Assessment'!A67</f>
-        <v>0</v>
-      </c>
+      <c r="A86" s="2"/>
     </row>
     <row r="87" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A87" s="2">
-        <f>'Table Assessment'!A68</f>
-        <v>0</v>
-      </c>
+      <c r="A87" s="2"/>
     </row>
     <row r="88" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A88" s="2">
-        <f>'Table Assessment'!A69</f>
-        <v>0</v>
-      </c>
+      <c r="A88" s="2"/>
     </row>
     <row r="89" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A89" s="2">
-        <f>'Table Assessment'!A70</f>
-        <v>0</v>
-      </c>
+      <c r="A89" s="2"/>
     </row>
     <row r="90" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A90" s="2">
-        <f>'Table Assessment'!A71</f>
-        <v>0</v>
-      </c>
+      <c r="A90" s="2"/>
     </row>
     <row r="91" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A91" s="2">
-        <f>'Table Assessment'!A72</f>
-        <v>0</v>
-      </c>
+      <c r="A91" s="2"/>
     </row>
     <row r="92" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A92" s="2">
-        <f>'Table Assessment'!A73</f>
-        <v>0</v>
-      </c>
+      <c r="A92" s="2"/>
     </row>
     <row r="93" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A93" s="2">
-        <f>'Table Assessment'!A74</f>
-        <v>0</v>
-      </c>
+      <c r="A93" s="2"/>
     </row>
     <row r="94" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A94" s="2">
-        <f>'Table Assessment'!A75</f>
-        <v>0</v>
-      </c>
+      <c r="A94" s="2"/>
     </row>
     <row r="95" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A95" s="2">
-        <f>'Table Assessment'!A76</f>
-        <v>0</v>
-      </c>
+      <c r="A95" s="2"/>
     </row>
     <row r="96" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A96" s="2">
-        <f>'Table Assessment'!A77</f>
-        <v>0</v>
-      </c>
+      <c r="A96" s="2"/>
     </row>
     <row r="97" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A97" s="2">
-        <f>'Table Assessment'!A78</f>
-        <v>0</v>
-      </c>
+      <c r="A97" s="2"/>
     </row>
     <row r="98" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A98" s="2">
-        <f>'Table Assessment'!A79</f>
-        <v>0</v>
-      </c>
+      <c r="A98" s="2"/>
     </row>
     <row r="99" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A99" s="2">
-        <f>'Table Assessment'!A80</f>
-        <v>0</v>
-      </c>
+      <c r="A99" s="2"/>
     </row>
     <row r="100" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A100" s="2">
-        <f>'Table Assessment'!A81</f>
-        <v>0</v>
-      </c>
+      <c r="A100" s="2"/>
     </row>
     <row r="101" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A101" s="2">
-        <f>'Table Assessment'!A82</f>
-        <v>0</v>
-      </c>
+      <c r="A101" s="2"/>
     </row>
     <row r="102" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A102" s="2">
-        <f>'Table Assessment'!A83</f>
-        <v>0</v>
-      </c>
+      <c r="A102" s="2"/>
     </row>
     <row r="103" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A103" s="2">
-        <f>'Table Assessment'!A84</f>
-        <v>0</v>
-      </c>
+      <c r="A103" s="2"/>
     </row>
     <row r="104" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A104" s="2">
-        <f>'Table Assessment'!A85</f>
-        <v>0</v>
-      </c>
+      <c r="A104" s="2"/>
     </row>
     <row r="105" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A105" s="2">
-        <f>'Table Assessment'!A86</f>
-        <v>0</v>
-      </c>
+      <c r="A105" s="2"/>
     </row>
     <row r="106" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A106" s="2">
-        <f>'Table Assessment'!A87</f>
-        <v>0</v>
-      </c>
+      <c r="A106" s="2"/>
     </row>
     <row r="107" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A107" s="2">
-        <f>'Table Assessment'!A88</f>
-        <v>0</v>
-      </c>
+      <c r="A107" s="2"/>
     </row>
     <row r="108" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A108" s="2">
-        <f>'Table Assessment'!A89</f>
-        <v>0</v>
-      </c>
+      <c r="A108" s="2"/>
     </row>
     <row r="109" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A109" s="2">
-        <f>'Table Assessment'!A90</f>
-        <v>0</v>
-      </c>
+      <c r="A109" s="2"/>
     </row>
     <row r="110" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A110" s="2">
-        <f>'Table Assessment'!A91</f>
-        <v>0</v>
-      </c>
+      <c r="A110" s="2"/>
     </row>
     <row r="111" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A111" s="2">
-        <f>'Table Assessment'!A92</f>
-        <v>0</v>
-      </c>
+      <c r="A111" s="2"/>
     </row>
     <row r="112" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A112" s="2">
-        <f>'Table Assessment'!A93</f>
-        <v>0</v>
-      </c>
+      <c r="A112" s="2"/>
     </row>
     <row r="113" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A113" s="2">
-        <f>'Table Assessment'!A94</f>
-        <v>0</v>
-      </c>
+      <c r="A113" s="2"/>
     </row>
     <row r="114" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A114" s="2">
-        <f>'Table Assessment'!A95</f>
-        <v>0</v>
-      </c>
+      <c r="A114" s="2"/>
     </row>
     <row r="115" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A115" s="2">
-        <f>'Table Assessment'!A96</f>
-        <v>0</v>
-      </c>
+      <c r="A115" s="2"/>
     </row>
     <row r="116" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A116" s="2">
-        <f>'Table Assessment'!A97</f>
-        <v>0</v>
-      </c>
+      <c r="A116" s="2"/>
     </row>
     <row r="117" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A117" s="2">
-        <f>'Table Assessment'!A98</f>
-        <v>0</v>
-      </c>
+      <c r="A117" s="2"/>
     </row>
     <row r="118" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A118" s="2">
-        <f>'Table Assessment'!A99</f>
-        <v>0</v>
-      </c>
+      <c r="A118" s="2"/>
     </row>
     <row r="119" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A119" s="2">
-        <f>'Table Assessment'!A100</f>
-        <v>0</v>
-      </c>
+      <c r="A119" s="2"/>
     </row>
     <row r="120" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A120" s="2">
-        <f>'Table Assessment'!A101</f>
-        <v>0</v>
-      </c>
+      <c r="A120" s="2"/>
     </row>
     <row r="121" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A121" s="2">
-        <f>'Table Assessment'!A102</f>
-        <v>0</v>
-      </c>
+      <c r="A121" s="2"/>
     </row>
     <row r="122" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A122" s="2">
-        <f>'Table Assessment'!A103</f>
-        <v>0</v>
-      </c>
+      <c r="A122" s="2"/>
     </row>
     <row r="123" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A123" s="2">
-        <f>'Table Assessment'!A104</f>
-        <v>0</v>
-      </c>
+      <c r="A123" s="2"/>
     </row>
     <row r="124" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A124" s="2">
-        <f>'Table Assessment'!A105</f>
-        <v>0</v>
-      </c>
+      <c r="A124" s="2"/>
     </row>
     <row r="125" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A125" s="2">
-        <f>'Table Assessment'!A106</f>
-        <v>0</v>
-      </c>
+      <c r="A125" s="2"/>
     </row>
     <row r="126" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A126" s="2">
-        <f>'Table Assessment'!A107</f>
-        <v>0</v>
-      </c>
+      <c r="A126" s="2"/>
     </row>
     <row r="127" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A127" s="2">
-        <f>'Table Assessment'!A108</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A128" s="2">
-        <f>'Table Assessment'!A109</f>
-        <v>0</v>
-      </c>
+      <c r="A127" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
